--- a/KEEN 30m Subtidal Example/GOOS_EOV_Administrative_Info.xlsx
+++ b/KEEN 30m Subtidal Example/GOOS_EOV_Administrative_Info.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jebyrnes/Library/CloudStorage/GoogleDrive-jarrett.byrnes@gmail.com/.shortcut-targets-by-id/1uNfJ83WmlmCErHo4iUjWr1UYx8ZEmsih/Macroalgal EOV Data Processing docs/SOP_Visual/goos_data_sheets_and_entry_forms/KEEN 30m Subtidal Example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE64E4AE-1C4F-394B-8D4F-139359790531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3D405B-7564-B848-800D-A4949C020A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2180" windowWidth="27640" windowHeight="16940" xr2:uid="{3BB4A0A6-1544-394D-83A2-653BD8DB631A}"/>
+    <workbookView xWindow="4780" yWindow="1220" windowWidth="27640" windowHeight="16940" xr2:uid="{3BB4A0A6-1544-394D-83A2-653BD8DB631A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Organization Info" sheetId="1" r:id="rId1"/>
-    <sheet name="Observer Info" sheetId="3" r:id="rId2"/>
-    <sheet name="Metadata" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
+    <sheet name="Organization Info" sheetId="1" r:id="rId2"/>
+    <sheet name="Observer Info" sheetId="3" r:id="rId3"/>
+    <sheet name="Metadata" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
   <si>
     <t>Organisation</t>
   </si>
@@ -152,13 +153,64 @@
   </si>
   <si>
     <t>BYRNES</t>
+  </si>
+  <si>
+    <t>Dataset title</t>
+  </si>
+  <si>
+    <t>Shortname</t>
+  </si>
+  <si>
+    <t>License</t>
+  </si>
+  <si>
+    <t>Update frequency</t>
+  </si>
+  <si>
+    <t>Keywords</t>
+  </si>
+  <si>
+    <t>Keyword Thesaurus</t>
+  </si>
+  <si>
+    <t>Link to dataset if elsewhere</t>
+  </si>
+  <si>
+    <t>Sample Area WKT</t>
+  </si>
+  <si>
+    <t>Kelp Ecosystem Ecology Network Gulf of Maine Subtidal Sampling</t>
+  </si>
+  <si>
+    <t>keen_one</t>
+  </si>
+  <si>
+    <t>CC-By</t>
+  </si>
+  <si>
+    <t>Lots of text here about data set</t>
+  </si>
+  <si>
+    <t>Annual</t>
+  </si>
+  <si>
+    <t>http://temperatereefbase.imas.utas.edu.au/portal/search?uuid=a869dfaa-59a7-4d2f-aaa6-47c2dae5741a</t>
+  </si>
+  <si>
+    <t>POLYGON((-71.35269069418187 41.0102160917684, -71.00130121289968 43.402303708551294, -67.33367350201678 45.17937484824569, -66.32342874333045 44.759655134325484, -68.8929643252065 41.997518576958306, -69.52985776003048 40.910658579117644))</t>
+  </si>
+  <si>
+    <t>NASA Earthdata GCMD</t>
+  </si>
+  <si>
+    <t>kelp forest, coastal, brown algae, animals/invertebrates</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -210,6 +262,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -249,7 +308,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -269,9 +328,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -309,7 +368,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -415,7 +474,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -557,13 +616,92 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95ACA8BE-BA43-C548-B0E4-4A3F83263ABD}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BACB5F4-A3AB-E341-AE55-5B3792E26FCF}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -629,7 +767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4F1247-002D-9A4D-A2A0-47E335E9D3FE}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -651,24 +789,24 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -679,7 +817,7 @@
       <c r="B4">
         <v>35333</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" t="s">
         <v>31</v>
       </c>
     </row>
@@ -688,7 +826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6635EC42-3C58-AF48-8516-B9323009F78E}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/KEEN 30m Subtidal Example/GOOS_EOV_Administrative_Info.xlsx
+++ b/KEEN 30m Subtidal Example/GOOS_EOV_Administrative_Info.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jebyrnes/Library/CloudStorage/GoogleDrive-jarrett.byrnes@gmail.com/.shortcut-targets-by-id/1uNfJ83WmlmCErHo4iUjWr1UYx8ZEmsih/Macroalgal EOV Data Processing docs/SOP_Visual/goos_data_sheets_and_entry_forms/KEEN 30m Subtidal Example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3D405B-7564-B848-800D-A4949C020A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D2830B-1B64-8045-8E1B-638A84B6365A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="1220" windowWidth="27640" windowHeight="16940" xr2:uid="{3BB4A0A6-1544-394D-83A2-653BD8DB631A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
+    <sheet name="Dataset Info" sheetId="4" r:id="rId1"/>
     <sheet name="Organization Info" sheetId="1" r:id="rId2"/>
     <sheet name="Observer Info" sheetId="3" r:id="rId3"/>
     <sheet name="Metadata" sheetId="2" r:id="rId4"/>
